--- a/downloads/harmon-ridge-catalog.xlsx
+++ b/downloads/harmon-ridge-catalog.xlsx
@@ -456,6 +456,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3975,10 +3976,11 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Departments and course prefixes (enter these under Catalogist → Departments)</t>
-        </is>
-      </c>
-    </row>
+          <t>Departments and course prefixes (enter these under Vessera → Departments)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -4110,10 +4112,11 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Programs (enter each under Catalogist → Add New Program)</t>
-        </is>
-      </c>
-    </row>
+          <t>Programs (enter each under Vessera → Add New Program)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -4911,6 +4914,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -4984,7 +4988,6 @@
           <t>CSS 101 College Success Skills</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>1</v>
       </c>
@@ -5020,7 +5023,6 @@
           <t>CIS 101 Computer Concepts</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>3</v>
       </c>
@@ -5056,7 +5058,6 @@
           <t>CIS 110 Programming Fundamentals</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>3</v>
       </c>
@@ -5092,7 +5093,6 @@
           <t>CIS 115 Web Development I</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>3</v>
       </c>
@@ -5128,7 +5128,6 @@
           <t>ENG 101 English Composition I</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>3</v>
       </c>
@@ -5189,14 +5188,11 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" s="4" t="n">
         <v>16</v>
       </c>
@@ -5232,7 +5228,6 @@
           <t>CIS 120 Database Fundamentals</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>3</v>
       </c>
@@ -5268,7 +5263,6 @@
           <t>CIS 125 Python Programming</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>3</v>
       </c>
@@ -5304,7 +5298,6 @@
           <t>CIS 130 Java Programming I</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>3</v>
       </c>
@@ -5340,7 +5333,6 @@
           <t>CIS 140 Web Development II</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>3</v>
       </c>
@@ -5401,14 +5393,11 @@
           <t>Semester 2</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" s="4" t="n">
         <v>15</v>
       </c>
@@ -5444,7 +5433,6 @@
           <t>CIS 150 Database Programming</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>3</v>
       </c>
@@ -5480,7 +5468,6 @@
           <t>CIS 155 Mobile App Development</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>3</v>
       </c>
@@ -5516,7 +5503,6 @@
           <t>CIS 160 Systems Analysis and Design</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>3</v>
       </c>
@@ -5552,7 +5538,6 @@
           <t>CIS 210 Java Programming II</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>3</v>
       </c>
@@ -5613,14 +5598,11 @@
           <t>Semester 3</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" s="4" t="n">
         <v>15</v>
       </c>
@@ -5656,7 +5638,6 @@
           <t>CIS 250 Software Development Capstone</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>3</v>
       </c>
@@ -5732,7 +5713,6 @@
           <t>CIS 215 Full-Stack Web Development</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>3</v>
       </c>
@@ -5768,7 +5748,6 @@
           <t>CIS 230 Cloud Application Development</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>3</v>
       </c>
@@ -5804,7 +5783,6 @@
           <t>CIS 240 Data Analytics</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>3</v>
       </c>
@@ -5840,7 +5818,6 @@
           <t>CIS 260 Secure Coding</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>3</v>
       </c>
@@ -5876,7 +5853,6 @@
           <t>NET 150 Network Security Fundamentals</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>3</v>
       </c>
@@ -5912,7 +5888,6 @@
           <t>CIS 220 Software Testing</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>3</v>
       </c>
@@ -5933,14 +5908,11 @@
           <t>Semester 4</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr">
         <is>
           <t>Web and Cloud 16 / Cybersecurity 16</t>
@@ -5978,7 +5950,6 @@
           <t>CSS 101 College Success Skills</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>1</v>
       </c>
@@ -6014,7 +5985,6 @@
           <t>CIS 101 Computer Concepts</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>3</v>
       </c>
@@ -6050,7 +6020,6 @@
           <t>CIS 110 Programming Fundamentals</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>3</v>
       </c>
@@ -6086,7 +6055,6 @@
           <t>CIS 115 Web Development I</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>3</v>
       </c>
@@ -6122,7 +6090,6 @@
           <t>BUS 120 Office Applications</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>3</v>
       </c>
@@ -6143,14 +6110,11 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" s="4" t="n">
         <v>13</v>
       </c>
@@ -6186,7 +6150,6 @@
           <t>CIS 120 Database Fundamentals</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>3</v>
       </c>
@@ -6222,7 +6185,6 @@
           <t>CIS 125 Python Programming</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>3</v>
       </c>
@@ -6258,7 +6220,6 @@
           <t>CIS 130 Java Programming I</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>3</v>
       </c>
@@ -6294,7 +6255,6 @@
           <t>CIS 140 Web Development II</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>3</v>
       </c>
@@ -6355,14 +6315,11 @@
           <t>Semester 2</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" s="4" t="n">
         <v>15</v>
       </c>
@@ -6398,7 +6355,6 @@
           <t>CSS 101 College Success Skills</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>1</v>
       </c>
@@ -6434,7 +6390,6 @@
           <t>NET 101 IT Essentials</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>3</v>
       </c>
@@ -6470,7 +6425,6 @@
           <t>NET 110 Networking Fundamentals</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>3</v>
       </c>
@@ -6506,7 +6460,6 @@
           <t>CIS 101 Computer Concepts</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>3</v>
       </c>
@@ -6542,7 +6495,6 @@
           <t>ENG 101 English Composition I</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>3</v>
       </c>
@@ -6603,14 +6555,11 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" s="4" t="n">
         <v>16</v>
       </c>
@@ -6646,7 +6595,6 @@
           <t>NET 120 Operating Systems</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>3</v>
       </c>
@@ -6682,7 +6630,6 @@
           <t>NET 140 Routing and Switching</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>3</v>
       </c>
@@ -6718,7 +6665,6 @@
           <t>NET 150 Network Security Fundamentals</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>3</v>
       </c>
@@ -6754,7 +6700,6 @@
           <t>CIS 110 Programming Fundamentals</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>3</v>
       </c>
@@ -6815,14 +6760,11 @@
           <t>Semester 2</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" s="4" t="n">
         <v>15</v>
       </c>
@@ -6858,7 +6800,6 @@
           <t>NET 130 Linux Administration</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>3</v>
       </c>
@@ -6894,7 +6835,6 @@
           <t>NET 210 Windows Server Administration</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>3</v>
       </c>
@@ -6930,7 +6870,6 @@
           <t>NET 240 Wireless Networking</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>3</v>
       </c>
@@ -6966,7 +6905,6 @@
           <t>CIS 120 Database Fundamentals</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>3</v>
       </c>
@@ -7027,14 +6965,11 @@
           <t>Semester 3</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" s="4" t="n">
         <v>15</v>
       </c>
@@ -7070,7 +7005,6 @@
           <t>NET 220 Cloud Infrastructure</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>3</v>
       </c>
@@ -7106,7 +7040,6 @@
           <t>NET 230 Ethical Hacking</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>3</v>
       </c>
@@ -7142,7 +7075,6 @@
           <t>NET 250 Network Technology Capstone</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>3</v>
       </c>
@@ -7178,7 +7110,6 @@
           <t>NET 290 Network Technology Internship</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>3</v>
       </c>
@@ -7239,14 +7170,11 @@
           <t>Semester 4</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" s="4" t="n">
         <v>16</v>
       </c>
@@ -7282,7 +7210,6 @@
           <t>CSS 101 College Success Skills</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>1</v>
       </c>
@@ -7318,7 +7245,6 @@
           <t>NET 101 IT Essentials</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>3</v>
       </c>
@@ -7354,7 +7280,6 @@
           <t>NET 110 Networking Fundamentals</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>3</v>
       </c>
@@ -7390,7 +7315,6 @@
           <t>CIS 101 Computer Concepts</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>3</v>
       </c>
@@ -7426,7 +7350,6 @@
           <t>MAT 105 Technical Mathematics</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>3</v>
       </c>
@@ -7447,14 +7370,11 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" s="4" t="n">
         <v>13</v>
       </c>
@@ -7490,7 +7410,6 @@
           <t>NET 120 Operating Systems</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>3</v>
       </c>
@@ -7526,7 +7445,6 @@
           <t>NET 140 Routing and Switching</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>3</v>
       </c>
@@ -7562,7 +7480,6 @@
           <t>NET 150 Network Security Fundamentals</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>3</v>
       </c>
@@ -7598,7 +7515,6 @@
           <t>CIS 110 Programming Fundamentals</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>3</v>
       </c>
@@ -7634,7 +7550,6 @@
           <t>CIS 120 Database Fundamentals</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>3</v>
       </c>
@@ -7655,14 +7570,11 @@
           <t>Semester 2</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" s="4" t="n">
         <v>15</v>
       </c>
@@ -7698,7 +7610,6 @@
           <t>WLD 101 Welding Safety and Fundamentals</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>2</v>
       </c>
@@ -7734,7 +7645,6 @@
           <t>WLD 110 Blueprint Reading for Welders</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>3</v>
       </c>
@@ -7770,7 +7680,6 @@
           <t>WLD 120 Shielded Metal Arc Welding I</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>4</v>
       </c>
@@ -7806,7 +7715,6 @@
           <t>WLD 130 Gas Metal Arc Welding</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>4</v>
       </c>
@@ -7842,7 +7750,6 @@
           <t>MAT 105 Technical Mathematics</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>3</v>
       </c>
@@ -7863,14 +7770,11 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" s="4" t="n">
         <v>16</v>
       </c>
@@ -7906,7 +7810,6 @@
           <t>WLD 125 Shielded Metal Arc Welding II</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>4</v>
       </c>
@@ -7942,7 +7845,6 @@
           <t>WLD 140 Gas Tungsten Arc Welding</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>4</v>
       </c>
@@ -7978,7 +7880,6 @@
           <t>WLD 150 Flux-Cored Arc Welding</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>4</v>
       </c>
@@ -8014,7 +7915,6 @@
           <t>WLD 160 Fabrication</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>4</v>
       </c>
@@ -8035,14 +7935,11 @@
           <t>Semester 2</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" s="4" t="n">
         <v>16</v>
       </c>
@@ -8078,7 +7975,6 @@
           <t>CSS 101 College Success Skills</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>1</v>
       </c>
@@ -8114,7 +8010,6 @@
           <t>BUS 101 Introduction to Business</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>3</v>
       </c>
@@ -8150,7 +8045,6 @@
           <t>BUS 120 Office Applications</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>3</v>
       </c>
@@ -8186,7 +8080,6 @@
           <t>ACC 101 Financial Accounting</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>3</v>
       </c>
@@ -8222,7 +8115,6 @@
           <t>ENG 101 English Composition I</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>3</v>
       </c>
@@ -8283,14 +8175,11 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" s="4" t="n">
         <v>16</v>
       </c>
@@ -8326,7 +8215,6 @@
           <t>BUS 110 Business Communications</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>3</v>
       </c>
@@ -8362,7 +8250,6 @@
           <t>BUS 130 Principles of Marketing</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>3</v>
       </c>
@@ -8398,7 +8285,6 @@
           <t>BUS 140 Customer Service</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>3</v>
       </c>
@@ -8434,7 +8320,6 @@
           <t>ACC 110 Payroll Accounting</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>3</v>
       </c>
@@ -8495,14 +8380,11 @@
           <t>Semester 2</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" s="4" t="n">
         <v>15</v>
       </c>
@@ -8538,7 +8420,6 @@
           <t>BUS 210 Small Business Management</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>3</v>
       </c>
@@ -8574,7 +8455,6 @@
           <t>BUS 220 Human Resource Management</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -8610,7 +8490,6 @@
           <t>ACC 201 Managerial Accounting</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>3</v>
       </c>
@@ -8646,7 +8525,6 @@
           <t>CIS 101 Computer Concepts</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>3</v>
       </c>
@@ -8707,14 +8585,11 @@
           <t>Semester 3</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" s="4" t="n">
         <v>15</v>
       </c>
@@ -8750,7 +8625,6 @@
           <t>BUS 230 Entrepreneurship</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>3</v>
       </c>
@@ -8786,7 +8660,6 @@
           <t>BUS 240 Business Law</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>3</v>
       </c>
@@ -8822,7 +8695,6 @@
           <t>ACC 210 Computerized Accounting</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>3</v>
       </c>
@@ -8858,7 +8730,6 @@
           <t>BUS 290 Business Internship</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>3</v>
       </c>
@@ -8919,14 +8790,11 @@
           <t>Semester 4</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
       <c r="H116" s="4" t="n">
         <v>16</v>
       </c>
@@ -8962,7 +8830,6 @@
           <t>CSS 101 College Success Skills</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>1</v>
       </c>
@@ -8998,7 +8865,6 @@
           <t>BUS 101 Introduction to Business</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>3</v>
       </c>
@@ -9034,7 +8900,6 @@
           <t>BUS 120 Office Applications</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>3</v>
       </c>
@@ -9070,7 +8935,6 @@
           <t>ACC 101 Financial Accounting</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>3</v>
       </c>
@@ -9106,7 +8970,6 @@
           <t>BUS 140 Customer Service</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>3</v>
       </c>
@@ -9127,14 +8990,11 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
       <c r="H122" s="4" t="n">
         <v>13</v>
       </c>
@@ -9170,7 +9030,6 @@
           <t>BUS 110 Business Communications</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
         <v>3</v>
       </c>
@@ -9206,7 +9065,6 @@
           <t>BUS 130 Principles of Marketing</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>3</v>
       </c>
@@ -9242,7 +9100,6 @@
           <t>ACC 110 Payroll Accounting</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>3</v>
       </c>
@@ -9278,7 +9135,6 @@
           <t>ACC 210 Computerized Accounting</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>3</v>
       </c>
@@ -9339,14 +9195,11 @@
           <t>Semester 2</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" s="4" t="n">
         <v>15</v>
       </c>
@@ -9382,7 +9235,6 @@
           <t>CSS 101 College Success Skills</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>1</v>
       </c>
@@ -9418,7 +9270,6 @@
           <t>AUT 101 Automotive Fundamentals</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>3</v>
       </c>
@@ -9454,7 +9305,6 @@
           <t>AUT 110 Brakes</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>4</v>
       </c>
@@ -9490,7 +9340,6 @@
           <t>AUT 130 Electrical Systems I</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>4</v>
       </c>
@@ -9526,7 +9375,6 @@
           <t>MAT 105 Technical Mathematics</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>3</v>
       </c>
@@ -9547,14 +9395,11 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
       <c r="H134" s="4" t="n">
         <v>15</v>
       </c>
@@ -9590,7 +9435,6 @@
           <t>AUT 120 Suspension and Steering</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>4</v>
       </c>
@@ -9626,7 +9470,6 @@
           <t>AUT 140 Engine Performance I</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>4</v>
       </c>
@@ -9662,7 +9505,6 @@
           <t>AUT 150 Engine Repair</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>4</v>
       </c>
@@ -9698,7 +9540,6 @@
           <t>ENG 101 English Composition I</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>3</v>
       </c>
@@ -9719,14 +9560,11 @@
           <t>Semester 2</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
       <c r="H139" s="4" t="n">
         <v>15</v>
       </c>
@@ -9762,7 +9600,6 @@
           <t>AUT 210 Electrical Systems II</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>4</v>
       </c>
@@ -9798,7 +9635,6 @@
           <t>AUT 220 Engine Performance II</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
         <v>4</v>
       </c>
@@ -9834,7 +9670,6 @@
           <t>AUT 230 Heating and Air Conditioning</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
         <v>3</v>
       </c>
@@ -9910,7 +9745,6 @@
           <t>BUS 140 Customer Service</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>3</v>
       </c>
@@ -9931,14 +9765,11 @@
           <t>Semester 3</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
       <c r="F145" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" s="4" t="n">
         <v>17</v>
       </c>
@@ -9974,7 +9805,6 @@
           <t>AUT 240 Automatic Transmissions</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>4</v>
       </c>
@@ -10090,7 +9920,6 @@
           <t>BUS 120 Office Applications</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>3</v>
       </c>
@@ -10111,14 +9940,11 @@
           <t>Semester 4</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
       <c r="F150" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" s="4" t="n">
         <v>14</v>
       </c>
@@ -10154,7 +9980,6 @@
           <t>CSS 101 College Success Skills</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
         <v>1</v>
       </c>
@@ -10190,7 +10015,6 @@
           <t>AUT 101 Automotive Fundamentals</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
         <v>3</v>
       </c>
@@ -10226,7 +10050,6 @@
           <t>AUT 110 Brakes</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
         <v>4</v>
       </c>
@@ -10262,7 +10085,6 @@
           <t>AUT 130 Electrical Systems I</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
         <v>4</v>
       </c>
@@ -10298,7 +10120,6 @@
           <t>MAT 105 Technical Mathematics</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
         <v>3</v>
       </c>
@@ -10319,14 +10140,11 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
       <c r="F156" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
       <c r="H156" s="4" t="n">
         <v>15</v>
       </c>
@@ -10362,7 +10180,6 @@
           <t>AUT 120 Suspension and Steering</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
         <v>4</v>
       </c>
@@ -10398,7 +10215,6 @@
           <t>AUT 140 Engine Performance I</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
         <v>4</v>
       </c>
@@ -10434,7 +10250,6 @@
           <t>AUT 150 Engine Repair</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
         <v>4</v>
       </c>
@@ -10470,7 +10285,6 @@
           <t>AUT 230 Heating and Air Conditioning</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
         <v>3</v>
       </c>
@@ -10491,14 +10305,11 @@
           <t>Semester 2</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
       <c r="F161" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr"/>
       <c r="H161" s="4" t="n">
         <v>15</v>
       </c>
@@ -10534,7 +10345,6 @@
           <t>CSS 101 College Success Skills</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
         <v>1</v>
       </c>
@@ -10570,7 +10380,6 @@
           <t>MED 101 Medical Terminology</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
         <v>3</v>
       </c>
@@ -10606,7 +10415,6 @@
           <t>MED 110 Anatomy and Physiology for Health Careers</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
         <v>3</v>
       </c>
@@ -10642,7 +10450,6 @@
           <t>MED 130 Medical Office Procedures</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
         <v>3</v>
       </c>
@@ -10678,7 +10485,6 @@
           <t>ENG 101 English Composition I</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
         <v>3</v>
       </c>
@@ -10739,14 +10545,11 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
       <c r="F168" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
       <c r="H168" s="4" t="n">
         <v>16</v>
       </c>
@@ -10782,7 +10585,6 @@
           <t>MED 120 Clinical Procedures I</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
         <v>4</v>
       </c>
@@ -10818,7 +10620,6 @@
           <t>MED 140 Pharmacology for Medical Assistants</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
         <v>3</v>
       </c>
@@ -10854,7 +10655,6 @@
           <t>MED 150 Phlebotomy</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
         <v>3</v>
       </c>
@@ -10875,14 +10675,11 @@
           <t>Semester 2</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
       <c r="F172" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
       <c r="H172" s="4" t="n">
         <v>10</v>
       </c>
@@ -10918,7 +10715,6 @@
           <t>MED 160 Clinical Procedures II</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
         <v>4</v>
       </c>
@@ -10954,7 +10750,6 @@
           <t>MED 190 Medical Assistant Externship</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
         <v>4</v>
       </c>
@@ -10975,14 +10770,11 @@
           <t>Semester 3</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
       <c r="F175" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
       <c r="H175" s="4" t="n">
         <v>8</v>
       </c>
@@ -11018,7 +10810,6 @@
           <t>CSS 101 College Success Skills</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
         <v>1</v>
       </c>
@@ -11054,7 +10845,6 @@
           <t>GRD 101 Design Principles</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
         <v>3</v>
       </c>
@@ -11090,7 +10880,6 @@
           <t>GRD 120 Digital Imaging</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
         <v>3</v>
       </c>
@@ -11126,7 +10915,6 @@
           <t>GRD 130 Vector Illustration</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
         <v>3</v>
       </c>
@@ -11162,7 +10950,6 @@
           <t>ENG 101 English Composition I</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
         <v>3</v>
       </c>
@@ -11223,14 +11010,11 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
       <c r="F182" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
       <c r="H182" s="4" t="n">
         <v>16</v>
       </c>
@@ -11266,7 +11050,6 @@
           <t>GRD 110 Typography</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
         <v>3</v>
       </c>
@@ -11302,7 +11085,6 @@
           <t>GRD 230 Motion Graphics</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
         <v>3</v>
       </c>
@@ -11338,7 +11120,6 @@
           <t>BUS 130 Principles of Marketing</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
         <v>3</v>
       </c>
@@ -11374,7 +11155,6 @@
           <t>CIS 115 Web Development I</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
         <v>3</v>
       </c>
@@ -11435,14 +11215,11 @@
           <t>Semester 2</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
       <c r="F188" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr"/>
       <c r="H188" s="4" t="n">
         <v>15</v>
       </c>
@@ -11478,7 +11255,6 @@
           <t>GRD 210 Web Graphics</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
         <v>3</v>
       </c>
@@ -11514,7 +11290,6 @@
           <t>GRD 220 Branding and Identity</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
         <v>3</v>
       </c>
@@ -11550,7 +11325,6 @@
           <t>GRD 140 Page Layout</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
         <v>3</v>
       </c>
@@ -11586,7 +11360,6 @@
           <t>CIS 140 Web Development II</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
         <v>3</v>
       </c>
@@ -11647,14 +11420,11 @@
           <t>Semester 3</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
       <c r="F194" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr"/>
       <c r="H194" s="4" t="n">
         <v>15</v>
       </c>
@@ -11690,7 +11460,6 @@
           <t>GRD 250 Portfolio Development</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
         <v>3</v>
       </c>
@@ -11726,7 +11495,6 @@
           <t>BUS 230 Entrepreneurship</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
         <v>3</v>
       </c>
@@ -11762,7 +11530,6 @@
           <t>BUS 120 Office Applications</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
         <v>3</v>
       </c>
@@ -11798,7 +11565,6 @@
           <t>ENG 102 English Composition II</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
         <v>3</v>
       </c>
@@ -11859,14 +11625,11 @@
           <t>Semester 4</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr"/>
       <c r="F200" s="4" t="inlineStr">
         <is>
           <t>Term total</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
       <c r="H200" s="4" t="n">
         <v>16</v>
       </c>
@@ -11895,10 +11658,11 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>General education template (build under Catalogist → Map Templates as "AAS General Education")</t>
-        </is>
-      </c>
-    </row>
+          <t>General education template (build under Vessera → Map Templates as "AAS General Education")</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -11942,7 +11706,6 @@
           <t>ENG 101 English Composition I</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>3</v>
       </c>
@@ -12067,7 +11830,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Harmon Ridge Technical College is a fictional college made up for Catalogist demonstrations and screenshots.</t>
+          <t>Harmon Ridge Technical College is a fictional college made up for Vessera demonstrations and screenshots.</t>
         </is>
       </c>
     </row>
@@ -12078,9 +11841,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -12091,21 +11852,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1. Departments sheet: add each department and its course prefixes under Catalogist → Departments.</t>
+          <t>1. Departments sheet: add each department and its course prefixes under Vessera → Departments.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2. Courses sheet: import it under Catalogist → Import Courses (header row 3; choose Publish immediately if you want them live).</t>
+          <t>2. Courses sheet: import it under Vessera → Import Courses (header row 3; choose Publish immediately if you want them live).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3. Gen Ed Template sheet: build the template under Catalogist → Map Templates.</t>
+          <t>3. Gen Ed Template sheet: build the template under Vessera → Map Templates.</t>
         </is>
       </c>
     </row>
